--- a/original/fr/french_talking_clock_audio_list.xlsx
+++ b/original/fr/french_talking_clock_audio_list.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <si>
     <t>Language</t>
   </si>
@@ -31,43 +31,154 @@
     <t>French</t>
   </si>
   <si>
-    <t>il_est.mp3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">il est</t>
-  </si>
-  <si>
-    <t>heures.pm3</t>
-  </si>
-  <si>
-    <t>heures</t>
-  </si>
-  <si>
-    <t>et.mp3</t>
-  </si>
-  <si>
-    <t>et</t>
-  </si>
-  <si>
-    <t>minutes.mp3</t>
-  </si>
-  <si>
-    <t>minutes</t>
-  </si>
-  <si>
-    <t>minuit.mp3</t>
-  </si>
-  <si>
-    <t>minuit</t>
-  </si>
-  <si>
-    <t>une.mp3</t>
+    <t>0h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">il est minuit</t>
+  </si>
+  <si>
+    <t>1h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">il est une heure</t>
+  </si>
+  <si>
+    <t>2h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">il est 2 heures</t>
+  </si>
+  <si>
+    <t>3h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">il est 3 heures</t>
+  </si>
+  <si>
+    <t>4h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">il est 4 heures</t>
+  </si>
+  <si>
+    <t>5h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">il est 5 heures</t>
+  </si>
+  <si>
+    <t>6h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">il est 6 heures</t>
+  </si>
+  <si>
+    <t>7h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">il est 7 heures</t>
+  </si>
+  <si>
+    <t>8h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">il est 8 heures</t>
+  </si>
+  <si>
+    <t>9h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">il est 9 heures</t>
+  </si>
+  <si>
+    <t>10h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">il est 10 heures</t>
+  </si>
+  <si>
+    <t>11h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">il est 11 heures</t>
+  </si>
+  <si>
+    <t>12h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">il est 12 heures</t>
+  </si>
+  <si>
+    <t>13h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">il est 13 heures</t>
+  </si>
+  <si>
+    <t>14h.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">il est 14 heures</t>
+  </si>
+  <si>
+    <t>15h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">il est 15 heures</t>
+  </si>
+  <si>
+    <t>16h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">il est 16 heures</t>
+  </si>
+  <si>
+    <t>17h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">il est 17 heures</t>
+  </si>
+  <si>
+    <t>18h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">il est 18 heures</t>
+  </si>
+  <si>
+    <t>19h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">il est 19 heures</t>
+  </si>
+  <si>
+    <t>20h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">il est 20 heures</t>
+  </si>
+  <si>
+    <t>21h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">il est 21 heures</t>
+  </si>
+  <si>
+    <t>22h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">il est 22 heures</t>
+  </si>
+  <si>
+    <t>23h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">il est 23 heures</t>
+  </si>
+  <si>
+    <t>1.mp3</t>
   </si>
   <si>
     <t>une</t>
-  </si>
-  <si>
-    <t>1.mp3</t>
   </si>
   <si>
     <t>2.mp3</t>
@@ -169,11 +280,17 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
       <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyProtection="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
       <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
@@ -659,7 +776,8 @@
   <cols>
     <col customWidth="1" min="1" max="1" style="0" width="11.529999999999999"/>
     <col customWidth="1" min="2" max="2" style="0" width="14.74"/>
-    <col customWidth="1" min="3" max="16384" style="0" width="11.529999999999999"/>
+    <col customWidth="1" min="3" max="3" style="0" width="15.7109375"/>
+    <col customWidth="1" min="4" max="16384" style="0" width="11.529999999999999"/>
   </cols>
   <sheetData>
     <row r="1" ht="15">
@@ -746,8 +864,8 @@
       <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C8">
-        <v>1</v>
+      <c r="C8" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="9" ht="15">
@@ -755,10 +873,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9">
-        <v>2</v>
+        <v>18</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="10" ht="15">
@@ -766,10 +884,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10">
-        <v>3</v>
+        <v>20</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="11" ht="15">
@@ -777,747 +895,945 @@
         <v>3</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11">
-        <v>4</v>
+        <v>22</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="12" ht="15">
       <c r="A12" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B12" t="str">
-        <f t="shared" ref="B12:B66" si="0">_xlfn.CONCAT(C12,".mp3")</f>
-        <v>5.mp3</v>
-      </c>
-      <c r="C12">
-        <v>5</v>
+      <c r="B12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="13" ht="15">
       <c r="A13" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>6.mp3</v>
-      </c>
-      <c r="C13">
-        <v>6</v>
+      <c r="B13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="14" ht="15">
       <c r="A14" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>7.mp3</v>
-      </c>
-      <c r="C14">
-        <v>7</v>
+      <c r="B14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="15" ht="15">
       <c r="A15" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>8.mp3</v>
-      </c>
-      <c r="C15">
-        <v>8</v>
+      <c r="B15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="16" ht="15">
       <c r="A16" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>9.mp3</v>
-      </c>
-      <c r="C16">
-        <v>9</v>
+      <c r="B16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="17" ht="15">
       <c r="A17" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B17" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>10.mp3</v>
-      </c>
-      <c r="C17">
-        <v>10</v>
+      <c r="B17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="18" ht="15">
       <c r="A18" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B18" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>11.mp3</v>
-      </c>
-      <c r="C18">
-        <v>11</v>
+      <c r="B18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="19" ht="15">
       <c r="A19" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B19" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>12.mp3</v>
-      </c>
-      <c r="C19">
-        <v>12</v>
+      <c r="B19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="20" ht="15">
       <c r="A20" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>13.mp3</v>
-      </c>
-      <c r="C20">
-        <v>13</v>
+      <c r="B20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="21" ht="15">
       <c r="A21" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B21" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>14.mp3</v>
-      </c>
-      <c r="C21">
-        <v>14</v>
+      <c r="B21" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="22" ht="15">
       <c r="A22" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B22" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>15.mp3</v>
-      </c>
-      <c r="C22">
-        <v>15</v>
+      <c r="B22" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="23" ht="15">
       <c r="A23" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B23" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>16.mp3</v>
-      </c>
-      <c r="C23">
-        <v>16</v>
+      <c r="B23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="24" ht="15">
       <c r="A24" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B24" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>17.mp3</v>
-      </c>
-      <c r="C24">
-        <v>17</v>
+      <c r="B24" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="25" ht="15">
       <c r="A25" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B25" s="2" t="str">
+      <c r="B25" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" ht="15">
+      <c r="A26" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" ht="15">
+      <c r="A27" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" ht="15">
+      <c r="A28" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" ht="15">
+      <c r="A29" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" ht="15">
+      <c r="A30" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B30" t="str">
+        <f t="shared" ref="B30:B84" si="0">_xlfn.CONCAT(C30,".mp3")</f>
+        <v>5.mp3</v>
+      </c>
+      <c r="C30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" ht="15">
+      <c r="A31" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B31" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>6.mp3</v>
+      </c>
+      <c r="C31">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" ht="15">
+      <c r="A32" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B32" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>7.mp3</v>
+      </c>
+      <c r="C32">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" ht="15">
+      <c r="A33" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B33" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>8.mp3</v>
+      </c>
+      <c r="C33">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" ht="15">
+      <c r="A34" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B34" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>9.mp3</v>
+      </c>
+      <c r="C34">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" ht="15">
+      <c r="A35" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B35" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>10.mp3</v>
+      </c>
+      <c r="C35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" ht="15">
+      <c r="A36" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B36" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>11.mp3</v>
+      </c>
+      <c r="C36">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" ht="15">
+      <c r="A37" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B37" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>12.mp3</v>
+      </c>
+      <c r="C37">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" ht="15">
+      <c r="A38" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B38" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>13.mp3</v>
+      </c>
+      <c r="C38">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" ht="15">
+      <c r="A39" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B39" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>14.mp3</v>
+      </c>
+      <c r="C39">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" ht="15">
+      <c r="A40" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B40" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>15.mp3</v>
+      </c>
+      <c r="C40">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" ht="15">
+      <c r="A41" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B41" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>16.mp3</v>
+      </c>
+      <c r="C41">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" ht="15">
+      <c r="A42" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B42" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>17.mp3</v>
+      </c>
+      <c r="C42">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" ht="15">
+      <c r="A43" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B43" s="4" t="str">
         <f t="shared" si="0"/>
         <v>18.mp3</v>
       </c>
-      <c r="C25">
+      <c r="C43">
         <v>18</v>
       </c>
     </row>
-    <row r="26" ht="15">
-      <c r="A26" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B26" s="2" t="str">
+    <row r="44" ht="15">
+      <c r="A44" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B44" s="4" t="str">
         <f t="shared" si="0"/>
         <v>19.mp3</v>
       </c>
-      <c r="C26">
+      <c r="C44">
         <v>19</v>
       </c>
     </row>
-    <row r="27" ht="15">
-      <c r="A27" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B27" s="2" t="str">
+    <row r="45" ht="15">
+      <c r="A45" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B45" s="4" t="str">
         <f t="shared" si="0"/>
         <v>20.mp3</v>
       </c>
-      <c r="C27">
+      <c r="C45">
         <v>20</v>
       </c>
     </row>
-    <row r="28" ht="15">
-      <c r="A28" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B28" s="2" t="str">
+    <row r="46" ht="15">
+      <c r="A46" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B46" s="4" t="str">
         <f t="shared" si="0"/>
         <v>21.mp3</v>
       </c>
-      <c r="C28">
+      <c r="C46">
         <v>21</v>
       </c>
     </row>
-    <row r="29" ht="15">
-      <c r="A29" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B29" s="2" t="str">
+    <row r="47" ht="15">
+      <c r="A47" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B47" s="4" t="str">
         <f t="shared" si="0"/>
         <v>22.mp3</v>
       </c>
-      <c r="C29">
+      <c r="C47">
         <v>22</v>
       </c>
     </row>
-    <row r="30" ht="15">
-      <c r="A30" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B30" s="2" t="str">
+    <row r="48" ht="15">
+      <c r="A48" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B48" s="4" t="str">
         <f t="shared" si="0"/>
         <v>23.mp3</v>
       </c>
-      <c r="C30">
+      <c r="C48">
         <v>23</v>
       </c>
     </row>
-    <row r="31" ht="15">
-      <c r="A31" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B31" s="2" t="str">
+    <row r="49" ht="15">
+      <c r="A49" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B49" s="4" t="str">
         <f t="shared" si="0"/>
         <v>24.mp3</v>
       </c>
-      <c r="C31">
+      <c r="C49">
         <v>24</v>
       </c>
     </row>
-    <row r="32" ht="15">
-      <c r="A32" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B32" s="2" t="str">
+    <row r="50" ht="15">
+      <c r="A50" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B50" s="4" t="str">
         <f t="shared" si="0"/>
         <v>25.mp3</v>
       </c>
-      <c r="C32">
+      <c r="C50">
         <v>25</v>
       </c>
     </row>
-    <row r="33" ht="15">
-      <c r="A33" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B33" s="2" t="str">
+    <row r="51" ht="15">
+      <c r="A51" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B51" s="4" t="str">
         <f t="shared" si="0"/>
         <v>26.mp3</v>
       </c>
-      <c r="C33">
+      <c r="C51">
         <v>26</v>
       </c>
     </row>
-    <row r="34" ht="15">
-      <c r="A34" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B34" s="2" t="str">
+    <row r="52" ht="15">
+      <c r="A52" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B52" s="4" t="str">
         <f t="shared" si="0"/>
         <v>27.mp3</v>
       </c>
-      <c r="C34">
+      <c r="C52">
         <v>27</v>
       </c>
     </row>
-    <row r="35" ht="15">
-      <c r="A35" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B35" s="2" t="str">
+    <row r="53" ht="15">
+      <c r="A53" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B53" s="4" t="str">
         <f t="shared" si="0"/>
         <v>28.mp3</v>
       </c>
-      <c r="C35">
+      <c r="C53">
         <v>28</v>
       </c>
     </row>
-    <row r="36" ht="15">
-      <c r="A36" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B36" s="2" t="str">
+    <row r="54" ht="15">
+      <c r="A54" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B54" s="4" t="str">
         <f t="shared" si="0"/>
         <v>29.mp3</v>
       </c>
-      <c r="C36">
+      <c r="C54">
         <v>29</v>
       </c>
     </row>
-    <row r="37" ht="15">
-      <c r="A37" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B37" s="2" t="str">
+    <row r="55" ht="15">
+      <c r="A55" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B55" s="4" t="str">
         <f t="shared" si="0"/>
         <v>30.mp3</v>
       </c>
-      <c r="C37">
+      <c r="C55">
         <v>30</v>
       </c>
     </row>
-    <row r="38" ht="15">
-      <c r="A38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B38" s="2" t="str">
+    <row r="56" ht="15">
+      <c r="A56" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B56" s="4" t="str">
         <f t="shared" si="0"/>
         <v>31.mp3</v>
       </c>
-      <c r="C38">
+      <c r="C56">
         <v>31</v>
       </c>
     </row>
-    <row r="39" ht="15">
-      <c r="A39" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B39" s="2" t="str">
+    <row r="57" ht="15">
+      <c r="A57" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B57" s="4" t="str">
         <f t="shared" si="0"/>
         <v>32.mp3</v>
       </c>
-      <c r="C39">
+      <c r="C57">
         <v>32</v>
       </c>
     </row>
-    <row r="40" ht="15">
-      <c r="A40" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B40" s="2" t="str">
+    <row r="58" ht="15">
+      <c r="A58" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B58" s="4" t="str">
         <f t="shared" si="0"/>
         <v>33.mp3</v>
       </c>
-      <c r="C40">
+      <c r="C58">
         <v>33</v>
       </c>
     </row>
-    <row r="41" ht="15">
-      <c r="A41" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B41" s="2" t="str">
+    <row r="59" ht="15">
+      <c r="A59" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B59" s="4" t="str">
         <f t="shared" si="0"/>
         <v>34.mp3</v>
       </c>
-      <c r="C41">
+      <c r="C59">
         <v>34</v>
       </c>
     </row>
-    <row r="42" ht="15">
-      <c r="A42" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B42" s="2" t="str">
+    <row r="60" ht="15">
+      <c r="A60" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B60" s="4" t="str">
         <f t="shared" si="0"/>
         <v>35.mp3</v>
       </c>
-      <c r="C42">
+      <c r="C60">
         <v>35</v>
       </c>
     </row>
-    <row r="43" ht="15">
-      <c r="A43" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B43" s="2" t="str">
+    <row r="61" ht="15">
+      <c r="A61" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B61" s="4" t="str">
         <f t="shared" si="0"/>
         <v>36.mp3</v>
       </c>
-      <c r="C43">
+      <c r="C61">
         <v>36</v>
       </c>
     </row>
-    <row r="44" ht="15">
-      <c r="A44" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B44" s="2" t="str">
+    <row r="62" ht="15">
+      <c r="A62" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B62" s="4" t="str">
         <f t="shared" si="0"/>
         <v>37.mp3</v>
       </c>
-      <c r="C44">
+      <c r="C62">
         <v>37</v>
       </c>
     </row>
-    <row r="45" ht="15">
-      <c r="A45" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B45" s="2" t="str">
+    <row r="63" ht="15">
+      <c r="A63" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B63" s="4" t="str">
         <f t="shared" si="0"/>
         <v>38.mp3</v>
       </c>
-      <c r="C45">
+      <c r="C63">
         <v>38</v>
       </c>
     </row>
-    <row r="46" ht="15">
-      <c r="A46" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B46" s="2" t="str">
+    <row r="64" ht="15">
+      <c r="A64" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B64" s="4" t="str">
         <f t="shared" si="0"/>
         <v>39.mp3</v>
       </c>
-      <c r="C46">
+      <c r="C64">
         <v>39</v>
       </c>
     </row>
-    <row r="47" ht="15">
-      <c r="A47" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B47" s="2" t="str">
+    <row r="65" ht="15">
+      <c r="A65" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B65" s="4" t="str">
         <f t="shared" si="0"/>
         <v>40.mp3</v>
       </c>
-      <c r="C47">
+      <c r="C65">
         <v>40</v>
       </c>
     </row>
-    <row r="48" ht="15">
-      <c r="A48" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B48" s="2" t="str">
+    <row r="66" ht="15">
+      <c r="A66" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B66" s="4" t="str">
         <f t="shared" si="0"/>
         <v>41.mp3</v>
       </c>
-      <c r="C48">
+      <c r="C66">
         <v>41</v>
       </c>
     </row>
-    <row r="49" ht="15">
-      <c r="A49" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B49" s="2" t="str">
+    <row r="67" ht="15">
+      <c r="A67" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B67" s="4" t="str">
         <f t="shared" si="0"/>
         <v>42.mp3</v>
       </c>
-      <c r="C49">
+      <c r="C67">
         <v>42</v>
       </c>
     </row>
-    <row r="50" ht="15">
-      <c r="A50" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B50" s="2" t="str">
+    <row r="68" ht="15">
+      <c r="A68" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B68" s="4" t="str">
         <f t="shared" si="0"/>
         <v>43.mp3</v>
       </c>
-      <c r="C50">
+      <c r="C68">
         <v>43</v>
       </c>
     </row>
-    <row r="51" ht="15">
-      <c r="A51" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B51" s="2" t="str">
+    <row r="69" ht="15">
+      <c r="A69" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B69" s="4" t="str">
         <f t="shared" si="0"/>
         <v>44.mp3</v>
       </c>
-      <c r="C51">
+      <c r="C69">
         <v>44</v>
       </c>
     </row>
-    <row r="52" ht="15">
-      <c r="A52" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B52" s="2" t="str">
+    <row r="70" ht="15">
+      <c r="A70" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B70" s="4" t="str">
         <f t="shared" si="0"/>
         <v>45.mp3</v>
       </c>
-      <c r="C52">
+      <c r="C70">
         <v>45</v>
       </c>
     </row>
-    <row r="53" ht="15">
-      <c r="A53" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B53" s="2" t="str">
+    <row r="71" ht="15">
+      <c r="A71" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B71" s="4" t="str">
         <f t="shared" si="0"/>
         <v>46.mp3</v>
       </c>
-      <c r="C53">
+      <c r="C71">
         <v>46</v>
       </c>
     </row>
-    <row r="54" ht="15">
-      <c r="A54" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B54" s="2" t="str">
+    <row r="72" ht="15">
+      <c r="A72" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B72" s="4" t="str">
         <f t="shared" si="0"/>
         <v>47.mp3</v>
       </c>
-      <c r="C54">
+      <c r="C72">
         <v>47</v>
       </c>
     </row>
-    <row r="55" ht="15">
-      <c r="A55" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B55" s="2" t="str">
+    <row r="73" ht="15">
+      <c r="A73" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B73" s="4" t="str">
         <f t="shared" si="0"/>
         <v>48.mp3</v>
       </c>
-      <c r="C55">
+      <c r="C73">
         <v>48</v>
       </c>
     </row>
-    <row r="56" ht="15">
-      <c r="A56" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B56" s="2" t="str">
+    <row r="74" ht="15">
+      <c r="A74" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B74" s="4" t="str">
         <f t="shared" si="0"/>
         <v>49.mp3</v>
       </c>
-      <c r="C56">
+      <c r="C74">
         <v>49</v>
       </c>
     </row>
-    <row r="57" ht="15">
-      <c r="A57" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B57" s="2" t="str">
+    <row r="75" ht="15">
+      <c r="A75" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B75" s="4" t="str">
         <f t="shared" si="0"/>
         <v>50.mp3</v>
       </c>
-      <c r="C57">
+      <c r="C75">
         <v>50</v>
       </c>
     </row>
-    <row r="58" ht="15">
-      <c r="A58" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B58" s="2" t="str">
+    <row r="76" ht="15">
+      <c r="A76" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B76" s="4" t="str">
         <f t="shared" si="0"/>
         <v>51.mp3</v>
       </c>
-      <c r="C58">
+      <c r="C76">
         <v>51</v>
       </c>
     </row>
-    <row r="59" ht="15">
-      <c r="A59" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B59" s="2" t="str">
+    <row r="77" ht="15">
+      <c r="A77" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B77" s="4" t="str">
         <f t="shared" si="0"/>
         <v>52.mp3</v>
       </c>
-      <c r="C59">
+      <c r="C77">
         <v>52</v>
       </c>
     </row>
-    <row r="60" ht="15">
-      <c r="A60" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B60" s="2" t="str">
+    <row r="78" ht="15">
+      <c r="A78" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B78" s="4" t="str">
         <f t="shared" si="0"/>
         <v>53.mp3</v>
       </c>
-      <c r="C60">
+      <c r="C78">
         <v>53</v>
       </c>
     </row>
-    <row r="61" ht="15">
-      <c r="A61" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B61" s="2" t="str">
+    <row r="79" ht="15">
+      <c r="A79" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B79" s="4" t="str">
         <f t="shared" si="0"/>
         <v>54.mp3</v>
       </c>
-      <c r="C61">
+      <c r="C79">
         <v>54</v>
       </c>
     </row>
-    <row r="62" ht="15">
-      <c r="A62" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B62" s="2" t="str">
+    <row r="80" ht="15">
+      <c r="A80" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B80" s="4" t="str">
         <f t="shared" si="0"/>
         <v>55.mp3</v>
       </c>
-      <c r="C62">
+      <c r="C80">
         <v>55</v>
       </c>
     </row>
-    <row r="63" ht="15">
-      <c r="A63" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B63" s="2" t="str">
+    <row r="81" ht="15">
+      <c r="A81" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B81" s="4" t="str">
         <f t="shared" si="0"/>
         <v>56.mp3</v>
       </c>
-      <c r="C63">
+      <c r="C81">
         <v>56</v>
       </c>
     </row>
-    <row r="64" ht="15">
-      <c r="A64" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B64" s="2" t="str">
+    <row r="82" ht="15">
+      <c r="A82" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B82" s="4" t="str">
         <f t="shared" si="0"/>
         <v>57.mp3</v>
       </c>
-      <c r="C64">
+      <c r="C82">
         <v>57</v>
       </c>
     </row>
-    <row r="65" ht="15">
-      <c r="A65" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B65" s="2" t="str">
+    <row r="83" ht="15">
+      <c r="A83" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B83" s="4" t="str">
         <f t="shared" si="0"/>
         <v>58.mp3</v>
       </c>
-      <c r="C65">
+      <c r="C83">
         <v>58</v>
       </c>
     </row>
-    <row r="66" ht="15">
-      <c r="A66" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B66" s="2" t="str">
+    <row r="84" ht="15">
+      <c r="A84" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B84" s="4" t="str">
         <f t="shared" si="0"/>
         <v>59.mp3</v>
       </c>
-      <c r="C66">
+      <c r="C84">
         <v>59</v>
       </c>
     </row>
-    <row r="67" ht="14.25">
-      <c r="A67" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B67" t="s">
-        <v>20</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="68" ht="14.25">
-      <c r="A68" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B68" t="s">
-        <v>22</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="69" ht="14.25">
-      <c r="A69" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B69" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="70" ht="14.25">
-      <c r="A70" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B70" t="s">
-        <v>26</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="71" ht="14.25">
-      <c r="A71" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B71" t="s">
-        <v>28</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="72" ht="14.25">
-      <c r="A72" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B72" t="s">
-        <v>30</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="73" ht="14.25">
-      <c r="A73" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B73" t="s">
-        <v>32</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>33</v>
+    <row r="85" ht="14.25">
+      <c r="A85" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B85" t="s">
+        <v>57</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="86" ht="14.25">
+      <c r="A86" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B86" t="s">
+        <v>59</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="87" ht="14.25">
+      <c r="A87" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B87" t="s">
+        <v>61</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="88" ht="14.25">
+      <c r="A88" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B88" t="s">
+        <v>63</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="89" ht="14.25">
+      <c r="A89" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B89" t="s">
+        <v>65</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="90" ht="14.25">
+      <c r="A90" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B90" t="s">
+        <v>67</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="91" ht="14.25">
+      <c r="A91" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B91" t="s">
+        <v>69</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
